--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="M23" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.89</v>
+        <v>3.96</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.39</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
-        <v>2.79</v>
+        <v>3.21</v>
       </c>
       <c r="N41" t="n">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.96</v>
+        <v>2.39</v>
       </c>
       <c r="M42" t="n">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>3.41</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.98</v>
+        <v>2.96</v>
       </c>
       <c r="M44" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N44" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N45" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.8</v>
+        <v>1.79</v>
       </c>
       <c r="M46" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.16</v>
+        <v>3.59</v>
       </c>
       <c r="N47" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="M49" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N49" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8921,10 +8921,10 @@
         <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M86" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.86</v>
+        <v>9</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="N88" t="n">
-        <v>3.59</v>
+        <v>1.3</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="M89" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="M90" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N90" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.46</v>
+        <v>3.13</v>
       </c>
       <c r="M91" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="N91" t="n">
-        <v>5.4</v>
+        <v>2.04</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB91" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="M94" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N94" t="n">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="M105" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13205,10 +13205,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.91</v>
+        <v>11.5</v>
       </c>
       <c r="M125" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="N125" t="n">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,16 +15341,16 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC125" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,10 +15454,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.21</v>
+        <v>8.5</v>
       </c>
       <c r="M127" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N127" t="n">
-        <v>3.34</v>
+        <v>1.4</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="M128" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N128" t="n">
-        <v>2.93</v>
+        <v>3.45</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,22 +15692,22 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC128" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M129" t="n">
         <v>3.15</v>
       </c>
-      <c r="M129" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N129" t="n">
-        <v>2.21</v>
+        <v>3.34</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M136" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N136" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G140" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="M20" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>1.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.33</v>
+        <v>3.96</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.72</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.96</v>
+        <v>2.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.11</v>
+        <v>2.96</v>
       </c>
       <c r="M36" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="N36" t="n">
-        <v>3.52</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.98</v>
+        <v>2.04</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M39" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.2</v>
+        <v>3.98</v>
       </c>
       <c r="M40" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="M42" t="n">
-        <v>2.79</v>
+        <v>3.85</v>
       </c>
       <c r="N42" t="n">
-        <v>3.41</v>
+        <v>1.62</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.96</v>
+        <v>2.11</v>
       </c>
       <c r="M44" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>3.52</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="N46" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="M60" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="N60" t="n">
-        <v>2.77</v>
+        <v>3.9</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N64" t="n">
-        <v>5.6</v>
+        <v>2.05</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N65" t="n">
-        <v>3.59</v>
+        <v>5.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8921,10 +8921,10 @@
         <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="M87" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N87" t="n">
-        <v>5.7</v>
+        <v>2.32</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N89" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="M90" t="n">
         <v>3.3</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="M91" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N91" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.9</v>
+        <v>1.28</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="N92" t="n">
-        <v>2.35</v>
+        <v>7.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,16 +11414,16 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="M94" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>6.3</v>
+        <v>2.04</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="M104" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N105" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13205,10 +13205,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="M119" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="N119" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M120" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N120" t="n">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="M121" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="M122" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="N122" t="n">
-        <v>2.21</v>
+        <v>2.93</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.63</v>
+        <v>8.5</v>
       </c>
       <c r="M126" t="n">
-        <v>2.87</v>
+        <v>4.3</v>
       </c>
       <c r="N126" t="n">
-        <v>2.93</v>
+        <v>1.4</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,16 +15454,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="M127" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N127" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M136" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N136" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB136" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M137" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.39</v>
+        <v>1.86</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.98</v>
+        <v>5.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5.2</v>
+        <v>3.98</v>
       </c>
       <c r="M42" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.11</v>
+        <v>2.39</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="N44" t="n">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.76</v>
+        <v>1.79</v>
       </c>
       <c r="M45" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="M47" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="N47" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,16 +6059,16 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6181,7 +6181,7 @@
         <v>1.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N49" t="n">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N81" t="n">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="M82" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="N82" t="n">
-        <v>2.36</v>
+        <v>1.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="M87" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.13</v>
+        <v>1.55</v>
       </c>
       <c r="M89" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M91" t="n">
         <v>3.65</v>
       </c>
-      <c r="M91" t="n">
-        <v>3.05</v>
-      </c>
       <c r="N91" t="n">
-        <v>1.97</v>
+        <v>6.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11420,10 +11420,10 @@
         <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N98" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="M101" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="N101" t="n">
-        <v>1.3</v>
+        <v>1.97</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13205,10 +13205,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="M119" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N119" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="M120" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="N120" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N121" t="n">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>8.5</v>
+        <v>3.15</v>
       </c>
       <c r="M126" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="N126" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="N19" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>3.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.96</v>
+        <v>5.2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="M37" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="M38" t="n">
         <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>3.52</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.2</v>
+        <v>3.98</v>
       </c>
       <c r="M40" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.39</v>
+        <v>2.96</v>
       </c>
       <c r="M44" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="N44" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>1.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.16</v>
+        <v>3.59</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N48" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.8</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.34</v>
+        <v>1.57</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>1.95</v>
+        <v>6.3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N85" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.13</v>
+        <v>2.13</v>
       </c>
       <c r="M86" t="n">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="N86" t="n">
-        <v>2.04</v>
+        <v>3.12</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="M87" t="n">
         <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>2.7</v>
+        <v>3.59</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N88" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="M98" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N98" t="n">
         <v>2.04</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="M101" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13205,10 +13205,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="M119" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="N119" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="M120" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="N120" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="M121" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>10.5</v>
+        <v>4.05</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.63</v>
+        <v>11.5</v>
       </c>
       <c r="M122" t="n">
-        <v>2.87</v>
+        <v>4.8</v>
       </c>
       <c r="N122" t="n">
-        <v>2.93</v>
+        <v>1.3</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14978,16 +14978,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>11.5</v>
+        <v>2.21</v>
       </c>
       <c r="M125" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="N125" t="n">
-        <v>1.3</v>
+        <v>3.34</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="M128" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N128" t="n">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,22 +15692,22 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="M129" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N129" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M136" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N136" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M138" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N138" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB138" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>2.95</v>
       </c>
       <c r="M19" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.95</v>
+        <v>1.87</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="N20" t="n">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.2</v>
+        <v>2.11</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>3.21</v>
       </c>
       <c r="N36" t="n">
-        <v>1.62</v>
+        <v>3.52</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.04</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="N37" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="M39" t="n">
-        <v>2.79</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>3.41</v>
+        <v>1.62</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.98</v>
+        <v>2.39</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>2.79</v>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>3.41</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>3.98</v>
       </c>
       <c r="M42" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N45" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.8</v>
+        <v>1.79</v>
       </c>
       <c r="M46" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="M47" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,16 +6059,16 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.16</v>
+        <v>3.59</v>
       </c>
       <c r="N48" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>2.76</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N49" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N59" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="N60" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>2.77</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="M63" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>2.77</v>
+        <v>3.9</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.25</v>
+        <v>1.46</v>
       </c>
       <c r="M64" t="n">
-        <v>3.13</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="M86" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.86</v>
+        <v>9</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="N87" t="n">
-        <v>3.59</v>
+        <v>1.3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="M88" t="n">
         <v>3.1</v>
       </c>
       <c r="N88" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N100" t="n">
-        <v>2.35</v>
+        <v>5.6</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>1.28</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="N101" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N103" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="M104" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="M123" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N123" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="M126" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="N126" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15573,10 +15573,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="M128" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N128" t="n">
-        <v>2.93</v>
+        <v>2.21</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,16 +15692,16 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="M129" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N129" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="AC129" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC130" t="n">
         <v>1.97</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC134" t="n">
         <v>1.57</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G140" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>2.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="M36" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.96</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="M38" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.2</v>
+        <v>2.96</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="N39" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="M40" t="n">
-        <v>2.79</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>3.41</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M45" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N46" t="n">
-        <v>4.5</v>
+        <v>1.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.59</v>
+        <v>3.16</v>
       </c>
       <c r="N48" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M59" t="n">
         <v>3.1</v>
       </c>
-      <c r="M59" t="n">
-        <v>3.23</v>
-      </c>
       <c r="N59" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.25</v>
+        <v>1.46</v>
       </c>
       <c r="M60" t="n">
-        <v>3.13</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="M61" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>2.77</v>
+        <v>3.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="N63" t="n">
-        <v>3.9</v>
+        <v>2.77</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="N64" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB64" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,16 +8558,16 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="M82" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="N82" t="n">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="M83" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="N83" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="M84" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N84" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M88" t="n">
         <v>3.1</v>
       </c>
       <c r="N88" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="M90" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="N90" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB90" t="n">
         <v>1.65</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.55</v>
+        <v>3.13</v>
       </c>
       <c r="M100" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N100" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.28</v>
+        <v>2.9</v>
       </c>
       <c r="M101" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="N101" t="n">
-        <v>7.8</v>
+        <v>2.35</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="M119" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N119" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="M120" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="N120" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N121" t="n">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>11.5</v>
+        <v>1.91</v>
       </c>
       <c r="M123" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N123" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,16 +15103,16 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="M124" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N124" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>8.5</v>
+        <v>2.63</v>
       </c>
       <c r="M126" t="n">
-        <v>4.3</v>
+        <v>2.87</v>
       </c>
       <c r="N126" t="n">
-        <v>1.4</v>
+        <v>2.93</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,16 +15454,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15573,10 +15573,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="M128" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="N128" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.21</v>
+        <v>11.5</v>
       </c>
       <c r="M129" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="N129" t="n">
-        <v>3.34</v>
+        <v>1.3</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>3.96</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="M20" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N36" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="M37" t="n">
         <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>3.52</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.11</v>
+        <v>3.98</v>
       </c>
       <c r="M38" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>1.96</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.2</v>
+        <v>2.04</v>
       </c>
       <c r="M40" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>1.62</v>
+        <v>3.8</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>3.59</v>
+        <v>3.16</v>
       </c>
       <c r="N46" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>4.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.16</v>
+        <v>3.59</v>
       </c>
       <c r="N48" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.34</v>
+        <v>1.57</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>6.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.31</v>
+        <v>3.65</v>
       </c>
       <c r="M63" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="N63" t="n">
-        <v>2.77</v>
+        <v>1.97</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="M64" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M65" t="n">
         <v>3.1</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.23</v>
-      </c>
       <c r="N65" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,16 +8558,16 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="M88" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="M90" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N90" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="M91" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N91" t="n">
-        <v>1.97</v>
+        <v>4.2</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="M92" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="N92" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N93" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.4</v>
+        <v>1.28</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="N94" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.07</v>
+        <v>1.4</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.4</v>
+        <v>1.86</v>
       </c>
       <c r="M95" t="n">
         <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>1.91</v>
+        <v>3.59</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="N96" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,16 +13080,16 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="M119" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="N119" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="M120" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N120" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="M123" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N123" t="n">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15097,22 +15097,22 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.21</v>
+        <v>11.5</v>
       </c>
       <c r="M124" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="N124" t="n">
-        <v>3.34</v>
+        <v>1.3</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="M125" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="N125" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,10 +15454,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>11.5</v>
+        <v>2.21</v>
       </c>
       <c r="M129" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="N129" t="n">
-        <v>1.3</v>
+        <v>3.34</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>1.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.86</v>
+        <v>2.39</v>
       </c>
       <c r="M36" t="n">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>3.41</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.98</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N38" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.04</v>
+        <v>3.98</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N45" t="n">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M46" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.59</v>
+        <v>3.16</v>
       </c>
       <c r="N48" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="M52" t="n">
-        <v>3.06</v>
+        <v>3.65</v>
       </c>
       <c r="N52" t="n">
-        <v>2.77</v>
+        <v>6.3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.57</v>
+        <v>3.34</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.65</v>
+        <v>2.31</v>
       </c>
       <c r="M63" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="N63" t="n">
-        <v>1.97</v>
+        <v>2.77</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N64" t="n">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N65" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="M66" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,16 +9986,16 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="M89" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N89" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M91" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N91" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.5</v>
+        <v>3.65</v>
       </c>
       <c r="M92" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="N92" t="n">
-        <v>5.7</v>
+        <v>1.97</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="M93" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.28</v>
+        <v>3.25</v>
       </c>
       <c r="M94" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="N94" t="n">
-        <v>7.8</v>
+        <v>2.15</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="M95" t="n">
         <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>3.59</v>
+        <v>1.91</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="M96" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,16 +13080,16 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,16 +13318,16 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M120" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N120" t="n">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="M121" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>10.5</v>
+        <v>4.05</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="M122" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N122" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15097,10 +15097,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>11.5</v>
+        <v>2.63</v>
       </c>
       <c r="M124" t="n">
-        <v>4.8</v>
+        <v>2.87</v>
       </c>
       <c r="N124" t="n">
-        <v>1.3</v>
+        <v>2.93</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15216,16 +15216,16 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="M125" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N125" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,16 +15698,16 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.21</v>
+        <v>8.5</v>
       </c>
       <c r="M129" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N129" t="n">
-        <v>3.34</v>
+        <v>1.4</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M137" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>1.72</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.33</v>
+        <v>3.96</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.39</v>
+        <v>1.86</v>
       </c>
       <c r="M36" t="n">
-        <v>2.79</v>
+        <v>3.21</v>
       </c>
       <c r="N36" t="n">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="N37" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>2.11</v>
       </c>
       <c r="M38" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>3.52</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.2</v>
+        <v>3.98</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="M41" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.04</v>
+        <v>5.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="M45" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="N45" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N46" t="n">
-        <v>4.5</v>
+        <v>1.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="N49" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="N60" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.1</v>
+        <v>1.46</v>
       </c>
       <c r="M65" t="n">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>2.05</v>
+        <v>5.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.8</v>
+        <v>3.34</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,16 +9986,16 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="M85" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="N85" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.5</v>
+        <v>3.15</v>
       </c>
       <c r="M91" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="N91" t="n">
-        <v>5.7</v>
+        <v>2.36</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.65</v>
+        <v>1.55</v>
       </c>
       <c r="M92" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N92" t="n">
-        <v>1.97</v>
+        <v>5.6</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N93" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="M102" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="N102" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,16 +13318,16 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="M124" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N124" t="n">
-        <v>2.93</v>
+        <v>2.21</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15216,16 +15216,16 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>11.5</v>
+        <v>1.91</v>
       </c>
       <c r="M125" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N125" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,16 +15341,16 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M126" t="n">
         <v>3.15</v>
       </c>
-      <c r="M126" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N126" t="n">
-        <v>2.21</v>
+        <v>3.34</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="M128" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N128" t="n">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,22 +15692,22 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>3.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.96</v>
+        <v>2.89</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.96</v>
+        <v>2.11</v>
       </c>
       <c r="M35" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>2.55</v>
+        <v>3.52</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.11</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.98</v>
+        <v>2.04</v>
       </c>
       <c r="M39" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="N44" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.76</v>
+        <v>1.79</v>
       </c>
       <c r="M45" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="M46" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>2.76</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="M56" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.96</v>
+        <v>9</v>
       </c>
       <c r="M58" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="N58" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="M60" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>6.3</v>
+        <v>2.04</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="M64" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>5.4</v>
+        <v>3.59</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB65" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="N66" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M77" t="n">
         <v>3.1</v>
       </c>
-      <c r="M77" t="n">
-        <v>3.23</v>
-      </c>
       <c r="N77" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="M82" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="M94" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N94" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="M102" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="M105" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,16 +13318,16 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>11.5</v>
+        <v>3.15</v>
       </c>
       <c r="M123" t="n">
-        <v>4.8</v>
+        <v>2.95</v>
       </c>
       <c r="N123" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.7</v>
+        <v>2.23</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.91</v>
+        <v>8.5</v>
       </c>
       <c r="M125" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N125" t="n">
-        <v>3.45</v>
+        <v>1.4</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,16 +15341,16 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC125" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>8.5</v>
+        <v>1.91</v>
       </c>
       <c r="M127" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N127" t="n">
-        <v>1.4</v>
+        <v>3.45</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,16 +15579,16 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.95</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.33</v>
+        <v>3.96</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="N23" t="n">
-        <v>2.89</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="N35" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>1.86</v>
       </c>
       <c r="M38" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.04</v>
+        <v>2.96</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5.2</v>
+        <v>2.04</v>
       </c>
       <c r="M42" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>1.62</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.98</v>
+        <v>5.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.23</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="M44" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N46" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="M47" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="N48" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N60" t="n">
-        <v>2.04</v>
+        <v>6.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.28</v>
+        <v>3.34</v>
       </c>
       <c r="M62" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>7.8</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="N69" t="n">
-        <v>6.3</v>
+        <v>3.12</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,16 +8796,16 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="M72" t="n">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="N72" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="M73" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N73" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="M75" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="N75" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="M76" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="M90" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N90" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="M104" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N105" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="M119" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="N119" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="M120" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N120" t="n">
-        <v>10.5</v>
+        <v>4.05</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="N121" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="M122" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N122" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>8.5</v>
+        <v>3.15</v>
       </c>
       <c r="M125" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="N125" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.91</v>
+        <v>8.5</v>
       </c>
       <c r="M127" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N127" t="n">
-        <v>3.45</v>
+        <v>1.4</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,16 +15579,16 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AB127" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC127" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="M128" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="N128" t="n">
-        <v>2.93</v>
+        <v>3.34</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,16 +15692,16 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB128" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>11.5</v>
+        <v>2.63</v>
       </c>
       <c r="M129" t="n">
-        <v>4.8</v>
+        <v>2.87</v>
       </c>
       <c r="N129" t="n">
-        <v>1.3</v>
+        <v>2.93</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15811,16 +15811,16 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M136" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N136" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB136" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M138" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI142"/>
+  <dimension ref="A1:AI140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46032.33333333334</v>
+        <v>46032.35416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46032.35416666666</v>
+        <v>46032.375</v>
       </c>
     </row>
     <row r="15">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.96</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46032.4375</v>
+        <v>46032.41666666666</v>
       </c>
     </row>
     <row r="30">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46032.45833333334</v>
+        <v>46032.4375</v>
       </c>
     </row>
     <row r="36">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.98</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="N36" t="n">
-        <v>1.96</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.86</v>
+        <v>2.39</v>
       </c>
       <c r="M38" t="n">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>3.41</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="M39" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="M41" t="n">
-        <v>2.79</v>
+        <v>3.85</v>
       </c>
       <c r="N41" t="n">
-        <v>3.41</v>
+        <v>1.62</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.11</v>
+        <v>2.96</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="N44" t="n">
-        <v>3.52</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46032.47916666666</v>
+        <v>46032.45833333334</v>
       </c>
     </row>
     <row r="46">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.76</v>
+        <v>1.79</v>
       </c>
       <c r="M46" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="M48" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="N48" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="N49" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="M50" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46032.5</v>
+        <v>46032.47916666666</v>
       </c>
     </row>
     <row r="51">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.13</v>
+        <v>3.65</v>
       </c>
       <c r="M69" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="N69" t="n">
-        <v>3.12</v>
+        <v>1.97</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,16 +8796,16 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.31</v>
+        <v>9</v>
       </c>
       <c r="M72" t="n">
-        <v>3.06</v>
+        <v>4.7</v>
       </c>
       <c r="N72" t="n">
-        <v>2.77</v>
+        <v>1.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.4</v>
+        <v>1.86</v>
       </c>
       <c r="M74" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N74" t="n">
-        <v>2.04</v>
+        <v>3.59</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="M75" t="n">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="N75" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.8</v>
+        <v>1.46</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N78" t="n">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N84" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12637,12 +12637,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="AI103" s="3" t="n">
-        <v>46032.51041666666</v>
+        <v>46032.5</v>
       </c>
     </row>
     <row r="104">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46032.52083333334</v>
+        <v>46032.51041666666</v>
       </c>
     </row>
     <row r="107">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46032.53125</v>
+        <v>46032.52083333334</v>
       </c>
     </row>
     <row r="110">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46032.54166666666</v>
+        <v>46032.53125</v>
       </c>
     </row>
     <row r="111">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46032.55208333334</v>
+        <v>46032.54166666666</v>
       </c>
     </row>
     <row r="114">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46032.5625</v>
+        <v>46032.55208333334</v>
       </c>
     </row>
     <row r="115">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14651,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="3" t="n">
-        <v>46032.58333333334</v>
+        <v>46032.5625</v>
       </c>
     </row>
     <row r="120">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="M121" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="N121" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M122" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="N122" t="n">
-        <v>3.45</v>
+        <v>6.3</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="AI122" s="3" t="n">
-        <v>46032.60416666666</v>
+        <v>46032.58333333334</v>
       </c>
     </row>
     <row r="123">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.21</v>
+        <v>11.5</v>
       </c>
       <c r="M128" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="N128" t="n">
-        <v>3.34</v>
+        <v>1.3</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="M130" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>9.6</v>
+        <v>3.34</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="AI130" s="3" t="n">
-        <v>46032.61458333334</v>
+        <v>46032.60416666666</v>
       </c>
     </row>
     <row r="131">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,16 +16055,16 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE131" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46032.625</v>
+        <v>46032.61458333334</v>
       </c>
     </row>
     <row r="132">
@@ -16207,12 +16207,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="AI133" s="3" t="n">
-        <v>46032.64583333334</v>
+        <v>46032.625</v>
       </c>
     </row>
     <row r="134">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.12</v>
+        <v>2.02</v>
       </c>
       <c r="M134" t="n">
-        <v>9.5</v>
+        <v>3.03</v>
       </c>
       <c r="N134" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,16 +16412,16 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.22</v>
+        <v>2.17</v>
       </c>
       <c r="AB134" t="n">
-        <v>3.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD134" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE134" t="n">
         <v>0</v>
@@ -16436,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="AI134" s="3" t="n">
-        <v>46032.66666666666</v>
+        <v>46032.64583333334</v>
       </c>
     </row>
     <row r="135">
@@ -16445,12 +16445,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="M135" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="N135" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,16 +16531,16 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.79</v>
+        <v>3.75</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD135" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE135" t="n">
         <v>0</v>
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="AI135" s="3" t="n">
-        <v>46032.69791666666</v>
+        <v>46032.66666666666</v>
       </c>
     </row>
     <row r="136">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="M136" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N136" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16674,7 +16674,7 @@
         <v>0</v>
       </c>
       <c r="AI136" s="3" t="n">
-        <v>46032.70833333334</v>
+        <v>46032.69791666666</v>
       </c>
     </row>
     <row r="137">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46032.875</v>
+        <v>46032.70833333334</v>
       </c>
     </row>
     <row r="140">
@@ -17040,12 +17040,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17150,244 +17150,6 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46032.875</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" t="n">
-        <v>0</v>
-      </c>
-      <c r="X141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI141" s="3" t="n">
-        <v>46032.875</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Wellington Phoenix</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Adelaide United</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M142" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N142" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI142" s="3" t="n">
         <v>46032.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46032.125</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46032.22916666666</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="N4" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46032.23263888889</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="M23" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>1.96</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.39</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="N38" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.11</v>
+        <v>3.98</v>
       </c>
       <c r="M42" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>3.52</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.96</v>
+        <v>2.11</v>
       </c>
       <c r="M44" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>3.52</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="N48" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="M49" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="N49" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.29</v>
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="M57" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>2.04</v>
+        <v>3.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="M69" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N69" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="M75" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="N75" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="N77" t="n">
-        <v>3.9</v>
+        <v>2.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.13</v>
+        <v>1.86</v>
       </c>
       <c r="M81" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>2.04</v>
+        <v>3.59</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="M82" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="N82" t="n">
-        <v>3.12</v>
+        <v>2.36</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="M85" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="N85" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="M87" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N87" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>6.3</v>
+        <v>1.91</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="M98" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="N98" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.25</v>
+        <v>2.13</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="N99" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB99" t="n">
         <v>1.65</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="M100" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.25</v>
+        <v>3.13</v>
       </c>
       <c r="M102" t="n">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="N102" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="M103" t="n">
         <v>3.1</v>
       </c>
       <c r="N103" t="n">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,16 +13318,16 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="M120" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="N120" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="M121" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>10.5</v>
+        <v>4.05</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="M122" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="N122" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="M123" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="N123" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>11.5</v>
+        <v>1.91</v>
       </c>
       <c r="M128" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N128" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,16 +15698,16 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB128" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="M129" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N129" t="n">
-        <v>2.93</v>
+        <v>2.21</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15811,16 +15811,16 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="N130" t="n">
-        <v>3.34</v>
+        <v>2.93</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M138" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N138" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB138" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>2.38</v>
@@ -704,10 +704,10 @@
         <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.64</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O4" t="n">
         <v>3.38</v>
@@ -942,10 +942,10 @@
         <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
         <v>2.38</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="N23" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="M37" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>2.39</v>
       </c>
       <c r="M38" t="n">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>3.41</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>3.98</v>
       </c>
       <c r="M39" t="n">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>1.96</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.39</v>
+        <v>2.11</v>
       </c>
       <c r="M43" t="n">
-        <v>2.79</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.11</v>
+        <v>2.96</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="N44" t="n">
-        <v>3.52</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N46" t="n">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.59</v>
+        <v>3.16</v>
       </c>
       <c r="N47" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="M48" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>3.6</v>
+        <v>2.29</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.76</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>2.76</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N50" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,16 +6416,16 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.65</v>
+        <v>2.31</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="N51" t="n">
-        <v>1.97</v>
+        <v>2.77</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.34</v>
+        <v>1.57</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N56" t="n">
-        <v>1.95</v>
+        <v>6.3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="N57" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="M75" t="n">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="M86" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="M87" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>2.32</v>
+        <v>3.59</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="M94" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N94" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>6.3</v>
+        <v>2.04</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M97" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N97" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.28</v>
+        <v>3.13</v>
       </c>
       <c r="M98" t="n">
-        <v>4.8</v>
+        <v>3.23</v>
       </c>
       <c r="N98" t="n">
-        <v>7.8</v>
+        <v>2.04</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.75</v>
+        <v>2.01</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="M99" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="M101" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>2.35</v>
+        <v>5.6</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="M102" t="n">
-        <v>3.23</v>
+        <v>2.82</v>
       </c>
       <c r="N102" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.96</v>
+        <v>2.9</v>
       </c>
       <c r="M103" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N103" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N105" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,16 +13318,16 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="M120" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="N120" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="M122" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="N122" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>8.5</v>
+        <v>3.15</v>
       </c>
       <c r="M123" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="N123" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>11.5</v>
+        <v>2.63</v>
       </c>
       <c r="M126" t="n">
-        <v>4.8</v>
+        <v>2.87</v>
       </c>
       <c r="N126" t="n">
-        <v>1.3</v>
+        <v>2.93</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,16 +15454,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB126" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.91</v>
+        <v>8.5</v>
       </c>
       <c r="M128" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N128" t="n">
-        <v>3.45</v>
+        <v>1.4</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,16 +15698,16 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AB128" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC128" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.15</v>
+        <v>11.5</v>
       </c>
       <c r="M129" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="N129" t="n">
-        <v>2.21</v>
+        <v>1.3</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI140"/>
+  <dimension ref="A1:AI141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,55 +659,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA2" t="n">
         <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC2" t="n">
         <v>2.64</v>
@@ -725,7 +725,7 @@
         <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46032.125</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O4" t="n">
         <v>3.38</v>
@@ -915,34 +915,34 @@
         <v>2.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
         <v>3.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
         <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
         <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
         <v>2.25</v>
@@ -951,19 +951,19 @@
         <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46032.23263888889</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46032.32291666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.95</v>
+        <v>2.37</v>
       </c>
       <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3.2</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46032.39583333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>2.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3.41</v>
+        <v>3.76</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P40" t="n">
         <v>2</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>3.98</v>
       </c>
       <c r="M42" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="M43" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="M46" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M47" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N48" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>2.76</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N49" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="M50" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="N50" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,16 +6416,16 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="M54" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.57</v>
+        <v>3.34</v>
       </c>
       <c r="M56" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M57" t="n">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="N57" t="n">
-        <v>2.8</v>
+        <v>5.23</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB57" t="n">
         <v>1.8</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46032.5</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46032.5</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46032.5</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>46032.5</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,73 +8870,73 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>46032.5</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M86" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M89" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="N89" t="n">
-        <v>7.8</v>
+        <v>2.32</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.15</v>
+        <v>1.57</v>
       </c>
       <c r="M94" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="N94" t="n">
-        <v>2.36</v>
+        <v>6.3</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N96" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.8</v>
+        <v>1.46</v>
       </c>
       <c r="M97" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N97" t="n">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,73 +12083,73 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="M98" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI98" s="3" t="n">
         <v>46032.5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="M100" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N100" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N106" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,16 +13318,16 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="N121" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="M122" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N122" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M123" t="n">
         <v>3.15</v>
       </c>
-      <c r="M123" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N123" t="n">
-        <v>2.21</v>
+        <v>3.34</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.91</v>
+        <v>8.5</v>
       </c>
       <c r="M124" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N124" t="n">
-        <v>3.45</v>
+        <v>1.4</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.63</v>
+        <v>11.5</v>
       </c>
       <c r="M126" t="n">
-        <v>2.87</v>
+        <v>4.8</v>
       </c>
       <c r="N126" t="n">
-        <v>2.93</v>
+        <v>1.3</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,16 +15454,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>8.5</v>
+        <v>2.63</v>
       </c>
       <c r="M128" t="n">
-        <v>4.3</v>
+        <v>2.87</v>
       </c>
       <c r="N128" t="n">
-        <v>1.4</v>
+        <v>2.93</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,16 +15692,16 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M139" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N139" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB139" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17040,116 +17040,235 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vis Pesaro</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" s="3" t="n">
+        <v>46032.875</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46032</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Australia A-League</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>Wellington Phoenix</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Adelaide United</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L140" t="n">
+      <c r="L141" t="n">
         <v>2.9</v>
       </c>
-      <c r="M140" t="n">
+      <c r="M141" t="n">
         <v>3.65</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N141" t="n">
         <v>2.2</v>
       </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="n">
         <v>1.58</v>
       </c>
-      <c r="AB140" t="n">
+      <c r="AB141" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" s="3" t="n">
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="3" t="n">
         <v>46032.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>3.96</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46032.39583333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>2.95</v>
       </c>
       <c r="M21" t="n">
         <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="O21" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>1.86</v>
       </c>
       <c r="M22" t="n">
         <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="N36" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.05</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="N38" t="n">
-        <v>3.76</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AC38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.2</v>
+        <v>2.04</v>
       </c>
       <c r="M41" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>3.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.98</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>3.76</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="N43" t="n">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.96</v>
+        <v>3.98</v>
       </c>
       <c r="M45" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N46" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.16</v>
+        <v>3.59</v>
       </c>
       <c r="N48" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="N49" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.8</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.34</v>
+        <v>1.57</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N56" t="n">
-        <v>1.95</v>
+        <v>6.3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46032.5</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46032.5</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.28</v>
+        <v>3.4</v>
       </c>
       <c r="M63" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>7.8</v>
+        <v>2.04</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="M64" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="N64" t="n">
-        <v>3.12</v>
+        <v>2.36</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.86</v>
+        <v>3.65</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>3.59</v>
+        <v>1.97</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M68" t="n">
         <v>3.13</v>
       </c>
-      <c r="M68" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N68" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O68" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB68" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB68" t="n">
-        <v>2</v>
-      </c>
       <c r="AC68" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46032.5</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>46032.5</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,73 +8870,73 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="N71" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="O71" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>46032.5</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46032.5</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46032.5</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N86" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,73 +10893,73 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI88" s="3" t="n">
         <v>46032.5</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,73 +11488,73 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI93" s="3" t="n">
         <v>46032.5</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,73 +11726,73 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI95" s="3" t="n">
         <v>46032.5</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.15</v>
+        <v>1.28</v>
       </c>
       <c r="M96" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="N96" t="n">
-        <v>2.36</v>
+        <v>7.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,16 +11890,16 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.51</v>
+        <v>2.75</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>5.4</v>
+        <v>3.59</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB97" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,73 +12083,73 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
         <v>46032.5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,73 +12440,73 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI101" s="3" t="n">
         <v>46032.5</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,16 +13318,16 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="M120" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="N120" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="M121" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M122" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N122" t="n">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="M123" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N123" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,16 +15103,16 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="M124" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N124" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="M128" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N128" t="n">
-        <v>2.93</v>
+        <v>2.21</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,16 +15692,16 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="M130" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N130" t="n">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,22 +15930,22 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC130" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G133" t="n">

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>2.37</v>
@@ -707,7 +707,7 @@
         <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.64</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="O4" t="n">
         <v>3.38</v>
@@ -942,7 +942,7 @@
         <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
         <v>2.25</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
         <v>2.38</v>
@@ -1418,10 +1418,10 @@
         <v>3.54</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
         <v>2.94</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>2.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.96</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.95</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
         <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.2</v>
       </c>
-      <c r="N22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.43</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.63</v>
+        <v>3.45</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>3.98</v>
       </c>
       <c r="M36" t="n">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>1.96</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>5.2</v>
       </c>
       <c r="M38" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.05</v>
+        <v>2.96</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="N42" t="n">
-        <v>3.76</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AC42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.2</v>
+        <v>1.95</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V44" t="n">
+        <v>8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.62</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.98</v>
+        <v>2.05</v>
       </c>
       <c r="M45" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>1.96</v>
+        <v>3.76</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="N46" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.8</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="M49" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="N49" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="M56" t="n">
-        <v>3.65</v>
+        <v>3.23</v>
       </c>
       <c r="N56" t="n">
-        <v>6.3</v>
+        <v>2.05</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="N60" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.31</v>
+        <v>9</v>
       </c>
       <c r="M66" t="n">
-        <v>3.06</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>2.77</v>
+        <v>1.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,55 +8751,55 @@
         </is>
       </c>
       <c r="L70" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB70" t="n">
         <v>1.8</v>
-      </c>
-      <c r="M70" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N70" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.64</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="M71" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="N71" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46032.5</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46032.5</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,73 +10893,73 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
         <v>46032.5</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,73 +11012,73 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>46032.5</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="M90" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="N90" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,73 +11250,73 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI91" s="3" t="n">
         <v>46032.5</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,73 +11488,73 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="M93" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="O93" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P93" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S93" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T93" t="n">
+        <v>3</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V93" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X93" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA93" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R93" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S93" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T93" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U93" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V93" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W93" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA93" t="n">
+      <c r="AB93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE93" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB93" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AI93" s="3" t="n">
         <v>46032.5</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,73 +11607,73 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI94" s="3" t="n">
         <v>46032.5</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,73 +11726,73 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI95" s="3" t="n">
         <v>46032.5</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="M96" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="N96" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,16 +11890,16 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,73 +11964,73 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.86</v>
+        <v>1.3</v>
       </c>
       <c r="M97" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="N97" t="n">
-        <v>3.59</v>
+        <v>7.8</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AI97" s="3" t="n">
         <v>46032.5</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,73 +12083,73 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI98" s="3" t="n">
         <v>46032.5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,73 +12202,73 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.34</v>
+        <v>2.22</v>
       </c>
       <c r="M99" t="n">
+        <v>3</v>
+      </c>
+      <c r="N99" t="n">
         <v>3.25</v>
       </c>
-      <c r="N99" t="n">
-        <v>1.95</v>
-      </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI99" s="3" t="n">
         <v>46032.5</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,73 +12321,73 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI100" s="3" t="n">
         <v>46032.5</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,73 +12440,73 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="M101" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>5.23</v>
+        <v>3.67</v>
       </c>
       <c r="O101" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="P101" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="R101" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S101" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="T101" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U101" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V101" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W101" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X101" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z101" t="n">
-        <v>3.12</v>
+        <v>3.52</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC101" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AG101" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH101" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AI101" s="3" t="n">
         <v>46032.5</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N102" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,73 +12678,73 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="M103" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N103" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA103" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI103" s="3" t="n">
         <v>46032.5</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N121" t="n">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="M122" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N122" t="n">
-        <v>10.5</v>
+        <v>4.05</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="M123" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="N123" t="n">
-        <v>3.45</v>
+        <v>2.21</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,16 +15103,16 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC123" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>11.5</v>
+        <v>1.91</v>
       </c>
       <c r="M124" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N124" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="M125" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N125" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,16 +15454,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="M128" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="N128" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>2.56</v>
       </c>
       <c r="M16" t="n">
-        <v>5.2</v>
+        <v>2.73</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>2.81</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,22 +2364,22 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.96</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46032.39583333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.63</v>
+        <v>3.84</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.33</v>
+        <v>2.69</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>3.96</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46032.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46032.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="M35" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.98</v>
+        <v>2.39</v>
       </c>
       <c r="M36" t="n">
-        <v>3.23</v>
+        <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>1.96</v>
+        <v>3.41</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="M37" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z37" t="n">
         <v>3.15</v>
       </c>
-      <c r="N37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46032.45833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.2</v>
+        <v>1.94</v>
       </c>
       <c r="M38" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="M43" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.05</v>
+        <v>5.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N45" t="n">
-        <v>3.76</v>
+        <v>1.62</v>
       </c>
       <c r="O45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M46" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.59</v>
+        <v>3.16</v>
       </c>
       <c r="N47" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5</v>
+        <v>1.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46032.5</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.38</v>
+        <v>2.2</v>
       </c>
       <c r="M60" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46032.5</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46032.5</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="N62" t="n">
-        <v>2.77</v>
+        <v>3.45</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46032.5</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>46032.5</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46032.5</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V69" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB69" t="n">
         <v>1.8</v>
       </c>
-      <c r="M69" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N69" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>46032.5</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="M70" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>46032.5</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46032.5</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,73 +10774,73 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI87" s="3" t="n">
         <v>46032.5</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,73 +11012,73 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N89" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="O89" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="P89" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="R89" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="S89" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="T89" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="U89" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="V89" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W89" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X89" t="n">
         <v>1.11</v>
       </c>
-      <c r="X89" t="n">
-        <v>1</v>
-      </c>
       <c r="Y89" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH89" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>1.33</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>46032.5</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,73 +11131,73 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.85</v>
+        <v>3.15</v>
       </c>
       <c r="M90" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N90" t="n">
-        <v>3.9</v>
+        <v>2.36</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI90" s="3" t="n">
         <v>46032.5</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,73 +11250,73 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI91" s="3" t="n">
         <v>46032.5</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,73 +11369,73 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="M92" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>6.3</v>
+        <v>2.32</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI92" s="3" t="n">
         <v>46032.5</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,73 +11488,73 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="M93" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N93" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="O93" t="n">
-        <v>3.65</v>
+        <v>4.12</v>
       </c>
       <c r="P93" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.02</v>
+        <v>2.72</v>
       </c>
       <c r="R93" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S93" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="U93" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V93" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="W93" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X93" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z93" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC93" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AI93" s="3" t="n">
         <v>46032.5</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,73 +11607,73 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI94" s="3" t="n">
         <v>46032.5</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="M96" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,73 +11964,73 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AI97" s="3" t="n">
         <v>46032.5</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,73 +12083,73 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
         <v>46032.5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,73 +12202,73 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI99" s="3" t="n">
         <v>46032.5</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,73 +12321,73 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U100" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI100" s="3" t="n">
         <v>46032.5</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,73 +12440,73 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI101" s="3" t="n">
         <v>46032.5</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.46</v>
+        <v>3.1</v>
       </c>
       <c r="M102" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="N102" t="n">
-        <v>5.4</v>
+        <v>2.05</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB102" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,73 +12678,73 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI103" s="3" t="n">
         <v>46032.5</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N106" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14701,73 +14701,73 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M120" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="N120" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG120" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH120" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AI120" s="3" t="n">
         <v>46032.58333333334</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,73 +14820,73 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="M121" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>10.5</v>
+        <v>4.05</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI121" s="3" t="n">
         <v>46032.58333333334</v>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,73 +14939,73 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M122" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N122" t="n">
-        <v>4.05</v>
+        <v>10.5</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>7.53</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA122" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI122" s="3" t="n">
         <v>46032.58333333334</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.15</v>
+        <v>1.91</v>
       </c>
       <c r="M123" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="N123" t="n">
-        <v>2.21</v>
+        <v>3.45</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,16 +15103,16 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.23</v>
+        <v>1.5</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,73 +15177,73 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="M124" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="N124" t="n">
-        <v>3.45</v>
+        <v>2.21</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.65</v>
+        <v>1.15</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI124" s="3" t="n">
         <v>46032.60416666666</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.63</v>
+        <v>11.5</v>
       </c>
       <c r="M126" t="n">
-        <v>2.87</v>
+        <v>4.8</v>
       </c>
       <c r="N126" t="n">
-        <v>2.93</v>
+        <v>1.3</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15454,16 +15454,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>8.5</v>
+        <v>2.63</v>
       </c>
       <c r="M128" t="n">
-        <v>4.3</v>
+        <v>2.87</v>
       </c>
       <c r="N128" t="n">
-        <v>1.4</v>
+        <v>2.93</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15692,16 +15692,16 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16605,73 +16605,73 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="M136" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N136" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V136" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W136" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AC136" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD136" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG136" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH136" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AI136" s="3" t="n">
         <v>46032.69791666666</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>

--- a/jogos_2026-01-10.xlsx
+++ b/jogos_2026-01-10.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46032.33333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1977,40 +1977,40 @@
         <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="AA13" t="n">
         <v>1.56</v>
@@ -2025,16 +2025,16 @@
         <v>1.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46032.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46032.375</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.95</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>3.96</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46032.39583333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.45</v>
+        <v>3.84</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.08</v>
+        <v>2.69</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46032.39583333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC21" t="n">
         <v>4.33</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AD21" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.72</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.96</v>
+        <v>2.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="M23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.2</v>
       </c>
-      <c r="N23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.43</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.63</v>
+        <v>3.45</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46032.39583333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46032.41666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46032.4375</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46032.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="M32" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
         <v>2.7</v>
       </c>
       <c r="O33" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.68</v>
+        <v>4.19</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="S33" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="T33" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V33" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46032.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,14 +4586,14 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="M35" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N35" t="n">
         <v>3.4</v>
       </c>
-      <c r="N35" t="n">
-        <v>3</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.79</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>3.41</v>
+        <v>1.62</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.97</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.32</v>
+        <v>2.94</v>
       </c>
       <c r="N37" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="O37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46032.45833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>2.39</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>3.41</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46032.45833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.96</v>
+        <v>2.11</v>
       </c>
       <c r="M43" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>3.52</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE43" t="n">
-        <v>0